--- a/Middleput/season2.xlsx
+++ b/Middleput/season2.xlsx
@@ -486,7 +486,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>Goals/Game</t>
+          <t>GoalxG</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
@@ -496,7 +496,7 @@
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>Points/Game</t>
+          <t>PointsxG</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">

--- a/Middleput/season2.xlsx
+++ b/Middleput/season2.xlsx
@@ -615,7 +615,7 @@
         <v>25</v>
       </c>
       <c r="P3" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="4">
@@ -625,7 +625,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C4" t="n">
         <v>2</v>
@@ -663,13 +663,13 @@
         <v>2</v>
       </c>
       <c r="N4" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="O4" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -679,7 +679,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C5" t="n">
         <v>2</v>
@@ -783,11 +783,11 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Andrea Scalambra</t>
+          <t>Wissam Rahal</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C7" t="n">
         <v>2</v>
@@ -810,7 +810,7 @@
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -825,23 +825,23 @@
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>9.5</v>
+        <v>10.5</v>
       </c>
       <c r="O7" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="P7" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Federico Paolucci</t>
+          <t>Andrea Scalambra</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C8" t="n">
         <v>2</v>
@@ -885,7 +885,7 @@
         <v>19</v>
       </c>
       <c r="P8" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -895,7 +895,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C9" t="n">
         <v>2</v>
@@ -939,17 +939,17 @@
         <v>19</v>
       </c>
       <c r="P9" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Wissam Rahal</t>
+          <t>Federico Paolucci</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C10" t="n">
         <v>2</v>
@@ -972,7 +972,7 @@
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -987,13 +987,13 @@
         <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>8</v>
+        <v>9.5</v>
       </c>
       <c r="O10" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="P10" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
